--- a/www/download/COUNTRY.CHN.zdW13.xlsx
+++ b/www/download/COUNTRY.CHN.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.35073066812331</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.31393434562861</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.2898114750299</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.27883125388176</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.27814537635583</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.27883126459024</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.27677527170928</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.27677525073227</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.27677538995426</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.27677526547708</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.19336325318561</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.97257413747067</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.60514071715928</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.9458916054178</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83139424738295</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>680.65</t>
+          <t>-0.442062615235115</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>689.5</t>
+          <t>-0.417311564605445</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>698.2</t>
+          <t>-0.442624142554934</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>706.37</t>
+          <t>-0.461032576023667</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>713.94</t>
+          <t>-0.469658005673531</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>720.85</t>
+          <t>-0.462246953591048</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>730.25</t>
+          <t>-0.422551365931953</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>737.4</t>
+          <t>-0.402395866957598</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>744.32</t>
+          <t>-0.381455097119571</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>-0.326817921991565</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>758.25</t>
+          <t>-0.291044522066011</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>-0.289224323740046</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>769.9</t>
+          <t>-0.228221103662421</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>774.8</t>
+          <t>-0.233612474279113</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>779.95</t>
+          <t>-0.211399892120848</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>230.89</t>
+          <t>-0.317006684540492</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>239.098</t>
+          <t>-0.278312178212826</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>247.449</t>
+          <t>-0.278303232240926</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>255.805</t>
+          <t>-0.274286064293841</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>264.115</t>
+          <t>-0.264195499555162</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>272.359</t>
+          <t>-0.236664771115092</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>281.876</t>
+          <t>-0.161973854977886</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>290.801</t>
+          <t>-0.114139150773344</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>299.812</t>
+          <t>-0.0444269707612603</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>309.298</t>
+          <t>0.0537996814959574</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>318.359</t>
+          <t>0.12132563598402</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>327.313</t>
+          <t>0.154493355642089</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>336.439</t>
+          <t>0.312253250309361</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>345.235</t>
+          <t>0.351464916203806</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>354.245</t>
+          <t>0.401391300657795</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1214994.346</t>
+          <t>-0.155319508636618</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1229546.798</t>
+          <t>-0.124872313344725</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1238180.551</t>
+          <t>-0.0761371674533422</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1236037.648</t>
+          <t>-0.0182567376250379</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1235342.034</t>
+          <t>0.0685853868287387</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1260851.623</t>
+          <t>0.175315838613953</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1339026.837</t>
+          <t>0.288897896645549</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1400107.894</t>
+          <t>0.400998666314165</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1440056.64</t>
+          <t>0.491508199695077</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1470748.352</t>
+          <t>0.514205942883522</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1476522.787</t>
+          <t>0.605560351192841</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1465602.046</t>
+          <t>0.683717991765843</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1492885.254</t>
+          <t>0.820783681833287</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1538102.906</t>
+          <t>0.846632635919972</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1555748.515</t>
+          <t>0.904210234001443</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>412150.393</t>
+          <t>1725219325362.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>426369.92</t>
+          <t>1778401585596.99</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>438823.592</t>
+          <t>1785624789533.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>447618.682</t>
+          <t>1788760089294.38</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>457002.426</t>
+          <t>1773854572366.88</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>476387.581</t>
+          <t>1764015652623.36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>516864.339</t>
+          <t>1805324823419.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>552146.561</t>
+          <t>1844118210794.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>580054.797</t>
+          <t>1962531215064.65</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>604918.813</t>
+          <t>2011843330397.64</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>619932.858</t>
+          <t>2122047376794.79</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>627893.215</t>
+          <t>2340062299766.25</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>652375.947</t>
+          <t>2457400029665.01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>685347.872</t>
+          <t>2558257728122.58</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>706605.398</t>
+          <t>2596542150413.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>529371285481.361</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>526690805308.109</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>527164760702.685</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>520172102125.903</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>505492465120.717</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>495215057360.946</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>495322702050.771</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>497726652527.186</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>491757306184.709</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>485733451241.381</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>473007590901.797</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>464216354086.268</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>436425087782.813</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>452843739404.218</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>453451598806.18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>21988632.091818</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>19314384.7102821</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>17382821.3757508</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>16743905.7190897</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.58</t>
+          <t>15463944.1399535</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>13843350.5649269</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>12836108.6142481</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>11951977.1555471</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>11346858.1547219</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>10379855.8001387</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>9288698.38322579</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>8083002.99752156</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>6588092.75967611</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>5308583.39363379</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>5056048.69221435</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>7990560.71270913</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.06</t>
+          <t>8070064.15778069</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>8075345.83209919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.62</t>
+          <t>7966801.95715463</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>8353120.60962133</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>38.23</t>
+          <t>8584419.71436284</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>8497599.95770357</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>8887265.66716479</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>9696486.06941191</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>10808013.6795989</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>11614515.4559062</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>12492148.7592579</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>14371972.8954692</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>16184482.2090982</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>15125484.0716397</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>14865298.1147575</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>15433223.7593341</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>15446193.1074034</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>15317223.7849036</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>15799680.9388509</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15971865.9055176</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>15874802.1451434</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>16569900.5176997</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>18904136.7938255</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>21315370.6845353</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>24080584.8257917</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>27721982.6120519</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>32801695.2495302</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>37385720.9536703</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>35372585.2605871</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>-0.221434172643992</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>-0.190473962938112</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45.27</t>
+          <t>-0.167577908907944</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>-0.139479644207825</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>-0.0959263347767534</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>-0.0380187891517342</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>0.0434901056130015</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>0.109336938131574</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>0.179555015415608</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>0.245371945356613</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>0.310619258511174</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0.352587450030988</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>0.494817701318855</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.513431262853195</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.558281854060263</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8.35073066812331</t>
+          <t>2292.74138493429</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.31393434562861</t>
+          <t>2202.82487013188</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.2898114750299</t>
+          <t>2130.39697273134</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.27883125388176</t>
+          <t>2033.47250484271</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.27814537635583</t>
+          <t>1913.91076573629</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.27883126459024</t>
+          <t>1818.2453653834</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.27677527170928</t>
+          <t>1757.23312047663</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.27677525073227</t>
+          <t>1711.57091150761</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.27677538995426</t>
+          <t>1640.21841560071</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8.27677526547708</t>
+          <t>1570.44037394726</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>8.19336325318561</t>
+          <t>1485.76864646511</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.97257413747067</t>
+          <t>1418.26488581823</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7.60514071715928</t>
+          <t>1297.19084969013</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.9458916054178</t>
+          <t>1311.69565464547</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6.83139424738295</t>
+          <t>1280.04907259467</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-122984381409.383</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>-105043694890.796</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>-102469147623.738</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>-94417854827.0893</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>-89164583803.0418</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>-93533393127.0405</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>-88810511219.5154</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>-97080820657.9827</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-117955346283.228</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-136676810670.246</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>-154506559288.143</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>-157812898638.842</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>-157070393537.316</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>-136777271557.733</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>-115025761721.406</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-123570956179.302</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>-105709910607.246</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>-105066719882.23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>-97533968925.9557</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>-92217872364.5073</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>-97388749203.5108</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>-93179158426.404</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>-102334745084.096</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-123346736890.818</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-142301383997.7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>-160182914784.798</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>-163497546663.628</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>-161937675617.175</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>-141729354930.677</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>-118990683456.332</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.127</t>
+          <t>586574769.919123</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.361</t>
+          <t>666215716.450431</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.489</t>
+          <t>2597572258.49262</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>3116114098.8664</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>3053288561.46547</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.815</t>
+          <t>3855356076.47029</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.982</t>
+          <t>4368647206.88857</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.159</t>
+          <t>5253924426.11332</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5391390607.59042</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>5624573327.45351</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>5676355496.65469</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>5684648024.78595</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5.606</t>
+          <t>4867282079.8586</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>7.133</t>
+          <t>4952083372.94378</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3964921734.9266</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.889</t>
+          <t>1785.05009327472</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.229</t>
+          <t>1783.24408745923</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.481</t>
+          <t>1773.38950289721</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>1749.84448336086</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.814</t>
+          <t>1730.31632088944</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>1749.11787821077</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>1833.65537447282</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.794</t>
+          <t>1898.70883436692</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.458</t>
+          <t>1934.72785849886</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5.373</t>
+          <t>1955.78238356927</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>6.527</t>
+          <t>1947.27700174926</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>1918.32728537736</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10.741</t>
+          <t>1939.06384410565</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>13.913</t>
+          <t>1985.16121108915</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>1994.67724213095</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>1785.05009327472</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>1783.24408745923</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>1773.38950289721</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1749.84448336086</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1730.31632088944</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.198</t>
+          <t>1749.11787821077</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1833.65537447282</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1898.70883436692</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1934.72785849886</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1955.78238356927</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.257</t>
+          <t>1947.27700174926</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>1918.32728537736</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>1939.06384410565</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>1985.16121108915</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.984</t>
+          <t>1994.67724213095</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-44.21</t>
+          <t>167973.661998802</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-41.73</t>
+          <t>171683.475331148</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-44.26</t>
+          <t>207238.754356267</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-46.1</t>
+          <t>207431.41559536</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-46.97</t>
+          <t>218500.671867043</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-46.22</t>
+          <t>279546.635422261</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-42.26</t>
+          <t>299418.561866264</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-40.24</t>
+          <t>365404.376202279</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-38.15</t>
+          <t>485016.140506976</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-32.68</t>
+          <t>655829.097530781</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-29.1</t>
+          <t>836718.788604738</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>1061578.03273553</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>1342004.10863597</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>1581532.9107827</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-21.14</t>
+          <t>1333217.07958759</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-31.7</t>
+          <t>143772965639.18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-27.83</t>
+          <t>126392809408.568</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-27.83</t>
+          <t>126556556122.204</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>120176787478.14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-26.42</t>
+          <t>117349676621.624</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>130206927987.497</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-16.2</t>
+          <t>129179156592.525</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>143124307213.045</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>176678135177.559</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>210059751505.171</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>242147141801.758</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>262350623104.204</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>275675994833.086</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>263065086722.67</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>221772243696.725</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>142146.183271598</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-12.49</t>
+          <t>143958.435637294</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>152472.930800699</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>152027.786600413</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>177255.904175995</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>234740.131105421</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>254919.042081741</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>308463.600901105</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>422020.14828747</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>570738.917504941</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>670058.922035534</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>802127.739298075</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>82.08</t>
+          <t>973630.835878624</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>84.66</t>
+          <t>1165162.30419468</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>1048884.49315057</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1214994.346</t>
+          <t>17229061103.1241</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1229546.798</t>
+          <t>17684184989.669</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1238180.551</t>
+          <t>17460313709.6755</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1236037.648</t>
+          <t>18647635464.2627</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1235342.034</t>
+          <t>22766626312.6354</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1260851.623</t>
+          <t>30713426992.5573</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1339026.837</t>
+          <t>34132065185.6213</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1400107.894</t>
+          <t>38151802285.4478</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1440056.64</t>
+          <t>50427848834.489</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1470748.352</t>
+          <t>63078816674.1178</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1476522.787</t>
+          <t>68949353562.6673</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1465602.046</t>
+          <t>77923931592.9097</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1492885.254</t>
+          <t>85162128340.2962</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1538102.906</t>
+          <t>92256506040.9351</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1555748.515</t>
+          <t>81153213114.6626</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>412150.393</t>
+          <t>25827.478727204</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>426369.92</t>
+          <t>27725.0396938538</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>438823.592</t>
+          <t>54765.8235555671</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>447618.682</t>
+          <t>55403.6289949468</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>457002.426</t>
+          <t>41244.7676910472</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>476387.581</t>
+          <t>44806.5043168395</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>516864.339</t>
+          <t>44499.519784523</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>552146.561</t>
+          <t>56940.7753011736</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>580054.797</t>
+          <t>62995.9922195069</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>604918.813</t>
+          <t>85090.1800258401</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>619932.858</t>
+          <t>166659.866569204</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>627893.215</t>
+          <t>259450.293437452</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>652375.947</t>
+          <t>368373.272757344</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>685347.872</t>
+          <t>416370.606588022</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>706605.398</t>
+          <t>284332.586437023</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1725219.325</t>
+          <t>126543904536.056</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1778401.586</t>
+          <t>108708624418.899</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1785624.79</t>
+          <t>109096242412.528</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1788760.089</t>
+          <t>101529152013.877</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1773854.572</t>
+          <t>94583050308.9884</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1764015.653</t>
+          <t>99493500994.9399</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1805324.823</t>
+          <t>95047091406.9037</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1844118.211</t>
+          <t>104972504927.597</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1962531.215</t>
+          <t>126250286343.07</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2011843.33</t>
+          <t>146980934831.054</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2122047.377</t>
+          <t>173197788239.09</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2340062.3</t>
+          <t>184426691511.294</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2457400.03</t>
+          <t>190513866492.79</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2558257.728</t>
+          <t>170808580681.734</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2596542.15</t>
+          <t>140619030582.063</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14.865</t>
+          <t>540949.76341</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15.433</t>
+          <t>637272.51759</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.446</t>
+          <t>698358.5122</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15.317</t>
+          <t>733353.7522</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>769416.261</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>15.972</t>
+          <t>845162.8223</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15.875</t>
+          <t>922030.66405</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>1001786.88916</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18.904</t>
+          <t>1126891.61132</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21.315</t>
+          <t>1338969.68842</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>24.081</t>
+          <t>1558738.41524</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>27.722</t>
+          <t>1858173.94652</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>32.802</t>
+          <t>2348695.72296</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>37.386</t>
+          <t>3032939.70854</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>35.373</t>
+          <t>3263395.75391</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>927359.119</t>
+          <t>0.155250260607999</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>929929.814</t>
+          <t>0.164471070154351</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>933533.435</t>
+          <t>0.175530029588369</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>930370.776</t>
+          <t>0.185001619803849</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>937817.747</t>
+          <t>0.192029041441894</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>948107.806</t>
+          <t>0.209751564099271</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>966369.722</t>
+          <t>0.22331803959739</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>989092.749</t>
+          <t>0.236329000655812</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1006639.806</t>
+          <t>0.251143636882645</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1020110.349</t>
+          <t>0.266230218982111</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1023503.052</t>
+          <t>0.284830668314102</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1054484.694</t>
+          <t>0.313680505245147</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1076703.09</t>
+          <t>0.361452255071653</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1107483.703</t>
+          <t>0.366697846078114</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1110293.654</t>
+          <t>0.410288418464595</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7.991</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>467727.886435222</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8.075</t>
+          <t>515800.335953662</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7.967</t>
+          <t>542539.536153294</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8.353</t>
+          <t>563860.76736749</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8.584</t>
+          <t>607903.674040208</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.498</t>
+          <t>659006.88251917</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8.887</t>
+          <t>707407.939686337</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>9.696</t>
+          <t>777143.095397519</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>10.808</t>
+          <t>900055.312694353</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>11.615</t>
+          <t>1018459.84835292</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>12.492</t>
+          <t>1182195.15416825</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>14.372</t>
+          <t>1468707.44826045</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>16.184</t>
+          <t>1905657.48987876</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15.125</t>
+          <t>2087894.22134836</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>529371.285</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>526690.805</t>
+          <t>467727.886435222</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>527164.761</t>
+          <t>515800.335953662</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>520172.102</t>
+          <t>542539.536153294</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>505492.465</t>
+          <t>563860.76736749</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>495215.057</t>
+          <t>607903.674040208</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>495322.702</t>
+          <t>659006.88251917</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>497726.653</t>
+          <t>707407.939686337</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>491757.306</t>
+          <t>777143.095397519</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>485733.451</t>
+          <t>900055.312694353</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>473007.591</t>
+          <t>1018459.84835292</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>464216.354</t>
+          <t>1182195.15416825</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>436425.088</t>
+          <t>1468707.44826045</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>452843.739</t>
+          <t>1905657.48987876</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>453451.599</t>
+          <t>2087894.22134836</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-22.14</t>
+          <t>2126558.60724414</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>2361413.11970726</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>2488756.12919788</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>2578115.65116243</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>2704997.60990416</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>2815277.64064881</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2981608.22690928</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>3158527.52731261</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>3439734.60767454</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>3874822.31367192</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>4348902.36244183</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>4880878.19600143</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>49.48</t>
+          <t>5606362.67948541</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>7132996.54979171</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>55.83</t>
+          <t>7059783.82168639</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21.989</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19.314</t>
+          <t>433774.526802564</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.383</t>
+          <t>469333.554400443</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16.744</t>
+          <t>494934.40106441</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15.464</t>
+          <t>520157.755393198</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13.843</t>
+          <t>550482.810170273</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12.836</t>
+          <t>581579.738494437</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.952</t>
+          <t>618128.386225982</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>11.347</t>
+          <t>662288.426450693</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>710753.382067819</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9.289</t>
+          <t>770227.835348201</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8.083</t>
+          <t>842411.169520139</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6.588</t>
+          <t>922864.559008487</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>5.309</t>
+          <t>1013220.98897476</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5.056</t>
+          <t>1098671.54916663</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>397856.131927165</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>433774.526802564</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>469333.554400443</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>494934.40106441</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>520157.755393198</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>550482.810170273</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>581579.738494437</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>618128.386225982</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>662288.426450693</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>710753.382067819</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>770227.835348201</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>842411.169520139</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>922864.559008487</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1013220.98897476</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1098671.54916663</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>330148.777972835</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>388384.142874778</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>436851.436996338</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>476955.571506706</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>519438.09813251</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>590508.888499792</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>665846.90408083</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>746451.654073663</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>863867.459282481</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1031594.79308565</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1238700.76632708</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1531036.33856175</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026432.43324955</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2615654.47089124</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2896547.53890164</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>412150392859.309</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>426369920378.008</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>438823592454.172</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>447618682394.545</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>457002425684.421</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>476387580510.376</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>516864338675.477</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>552146560740.986</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>580054796877.443</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>604918813097.261</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>619932858057.87</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>627893214636.227</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>652375946517.384</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>685347872401.688</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>706605398114.285</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1214994345987.44</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1229546798303.14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1238180550922.83</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1236037647711.61</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1235342034135.8</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1260851622508.23</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1339026837208.78</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1400107894462.17</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1440056639637.87</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1470748352444.09</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1476522786576.37</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1465602046028.31</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1492885253576.94</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1538102906351.87</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1555748515000.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>927359118910.789</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>929929813619.566</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>933533434522.381</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>930370776087.752</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>937817747349.174</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>948107806214.009</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>966369722461.129</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>989092749439.088</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1006639805625.82</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1020110349379.16</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1023503051701.24</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1054484694103.47</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1076703089611.7</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1107483703160.28</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1110293653915.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>680650000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>689500000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>698200000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>706370000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>713940000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>720850000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>730250000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>737400000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>744320000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>7.52e+08</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>758250000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>7.64e+08</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>769900000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>774800000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>779950000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>230890099.057785</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>239097902.1753</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>247449075.19598</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>255804836.74459</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>264114959.887512</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>272358762.348075</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>281876488.827175</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>290801070.04668</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>299812086.919296</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>309297608.0464</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>318358845.45495</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>327312872.742</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>336438611.08569</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>345235373.61768</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>354245480.51664</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1214994345987.44</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1229546798303.14</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1238180550922.83</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1236037647711.61</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1235342034135.8</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1260851622508.23</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1339026837208.78</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1400107894462.17</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1440056639637.87</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1470748352444.09</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1476522786576.37</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1465602046028.31</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1492885253576.94</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1538102906351.87</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1555748515000.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>412150392859.309</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>426369920378.008</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>438823592454.172</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>447618682394.545</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>457002425684.421</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>476387580510.376</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>516864338675.477</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>552146560740.986</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>580054796877.443</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>604918813097.261</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>619932858057.87</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>627893214636.227</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>652375946517.384</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>685347872401.688</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>706605398114.285</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.0562093506386633</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.060132898282147</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.0642229342975888</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.0684802104861104</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.0729051611681329</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.0774979069224905</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.082258260780203</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.0871857366777081</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.0972163267750453</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.102690348456082</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.11899884376754</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.134733325009745</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.131794604116846</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.140604669437637</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.140604669437637</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.443790668260678</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.452136418603582</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.460255196955978</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.4681321380586</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.475753011927834</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.483104273846828</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.490173109323406</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.496947473486285</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.485234087664569</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472155254567998</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.458939788004176</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.44538179323064</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.440040375197511</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.436009295706546</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.436009295706546</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.442857123957802</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.430587825971414</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.418379011603576</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.406244794312433</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.394198969761176</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.382254962087824</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.370425772753534</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.35872393269315</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.360406728417528</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.368011539833063</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.364918511085427</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.362742024616758</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.371022163542786</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.36624317771296</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.36624317771296</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0463005508328902</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0487470639722212</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0512995826534342</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0539610480363788</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.056734370862934</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0596224229662163</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0626280285504751</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0657539552756941</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.072556037345357</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0755835939356043</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0867325066632651</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.097428836119497</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.0941310138522617</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.100846173037866</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.100846173037866</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.440763305854076</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.446761572997244</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.452663377317704</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.458460645622173</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.46414528481011</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.469709201971289</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.475144325035073</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.48044262388356</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.471814324658347</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.461216139244906</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.450635553120864</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.439953048243381</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.435683855712475</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.43195168744715</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.43195168744715</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.455793286170177</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.447348505887678</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.438894182886005</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.430435449198591</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.421977487184099</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.413525517919637</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.405084789271595</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.396660563697889</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.398486780853439</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.406057409676632</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.405489083073014</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.405475258494265</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.413042273292406</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.410059282372126</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.410059282372126</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1888818.00833</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2229366.1548</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2480754.93414</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2647916.15531</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2814386.86818</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3125236.69535</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3454251.82819</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3794147.41702</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4457621.02152</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5372763.54888</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>6527489.8572</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8160175.32311</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>10740914.89603</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>13913136.42324</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15149964.83865</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>728004.9099</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>856112.02931</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>952651.77295</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1019495.10766</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1083298.8655</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1198412.56254</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1324853.7866</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1453859.59376</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1641010.55468</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1931650.10578</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2257160.61468</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2713231.49273</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3495139.88151</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4521311.96077</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4984441.76025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>17758318.2135344</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>18774740.1683004</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19731546.2433513</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>20612115.284853</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>21459490.3763524</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>22266287.2344285</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>23075895.8138145</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>23892605.1463974</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>24778920.3679366</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>25811464.7807498</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>26951756.7975726</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>28152579.7698671</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>29424285.0939325</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>30941003.0245525</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>32157310.8492424</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
